--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,53 +813,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>197290</v>
+        <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>102171</v>
+        <v>107865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>692</v>
+        <v>626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hårginst</t>
+          <t>Ljungögontröst</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Genista pilosa</t>
+          <t>Euphrasia micrantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mejeribacken, SSV om, Hl</t>
+          <t>Källshult NO, Gavelstensv. (2), Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394984</v>
+        <v>394577</v>
       </c>
       <c r="R3" t="n">
-        <v>6272917</v>
+        <v>6273839</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,22 +890,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Arkiv-N-Lah-0396</t>
+          <t>N-Lah-1996</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1998-06-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-06-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Medobservatör Jan-Erik Cederfelt. Ganska rikligt</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,85 +909,88 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Glänta</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Halland Floraväktarna</t>
+          <t>Lars-Erik Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Arne Hansson</t>
+          <t>Lars-Erik  Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Arkiv Floraväktarlokaler</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/197290</t>
+          <t>https://artportalen.se/Sighting/137284559</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>197291</v>
+        <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>102171</v>
+        <v>107865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>692</v>
+        <v>626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hårginst</t>
+          <t>Ljungögontröst</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Genista pilosa</t>
+          <t>Euphrasia micrantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mejeribacken, V om, Hl</t>
+          <t>Källshult NO, Kvarnvägen (2), Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394577</v>
+        <v>394995</v>
       </c>
       <c r="R4" t="n">
-        <v>6273572</v>
+        <v>6272892</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,22 +1014,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Arkiv-N-Lah-0424</t>
+          <t>N-Lah-1998</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1998-06-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1998-06-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Medobservatör Jan-Erik Cederfelt. Ganska rikligt</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,39 +1033,35 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsväg/kant</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Halland Floraväktarna</t>
+          <t>Lars-Erik Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Arne Hansson</t>
+          <t>Lars-Erik  Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Arkiv Floraväktarlokaler</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/197291</t>
+          <t>https://artportalen.se/Sighting/137284598</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>268280</v>
+        <v>197290</v>
       </c>
       <c r="B5" t="n">
         <v>102171</v>
@@ -1101,14 +1097,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dunkebjär, O om, skogsväg (2), Hl</t>
+          <t>Mejeribacken, SSV om, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394361</v>
+        <v>394984</v>
       </c>
       <c r="R5" t="n">
-        <v>6273189</v>
+        <v>6272917</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1135,22 +1131,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Arkiv-N-Lah-0406</t>
+          <t>Arkiv-N-Lah-0396</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-06-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Medobservatör Jan-Erik Cederfelt. Sparsamt</t>
+          <t>Medobservatör Jan-Erik Cederfelt. Ganska rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1160,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skogsväg</t>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1185,13 +1181,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/268280</t>
+          <t>https://artportalen.se/Sighting/197290</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>268582</v>
+        <v>197291</v>
       </c>
       <c r="B6" t="n">
         <v>102171</v>
@@ -1227,14 +1223,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dunkebjär, O om, skogsväg (1), Hl</t>
+          <t>Mejeribacken, V om, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394130</v>
+        <v>394577</v>
       </c>
       <c r="R6" t="n">
-        <v>6273287</v>
+        <v>6273572</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1261,22 +1257,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Arkiv-N-Lah-0410</t>
+          <t>Arkiv-N-Lah-0424</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-06-06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Medobservatör Jan-Erik Cederfelt. Sparsamt</t>
+          <t>Medobservatör Jan-Erik Cederfelt. Ganska rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,7 +1286,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Skogsväg/kant</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1311,13 +1307,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/268582</t>
+          <t>https://artportalen.se/Sighting/197291</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>268584</v>
+        <v>268280</v>
       </c>
       <c r="B7" t="n">
         <v>102171</v>
@@ -1353,14 +1349,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dunkebjär, O om, skogsväg (3), Hl</t>
+          <t>Dunkebjär, O om, skogsväg (2), Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394449</v>
+        <v>394361</v>
       </c>
       <c r="R7" t="n">
-        <v>6273360</v>
+        <v>6273189</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1387,7 +1383,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Arkiv-N-Lah-0416</t>
+          <t>Arkiv-N-Lah-0406</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1416,7 +1412,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Skogsväg, glänta</t>
+          <t>Skogsväg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1437,13 +1433,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/268584</t>
+          <t>https://artportalen.se/Sighting/268280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>268587</v>
+        <v>268582</v>
       </c>
       <c r="B8" t="n">
         <v>102171</v>
@@ -1479,14 +1475,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dunkebjär, NO om, O om Dunkebjär, skogsväg, Hl</t>
+          <t>Dunkebjär, O om, skogsväg (1), Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>393876</v>
+        <v>394130</v>
       </c>
       <c r="R8" t="n">
-        <v>6273684</v>
+        <v>6273287</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1513,7 +1509,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Arkiv-N-Lah-0426</t>
+          <t>Arkiv-N-Lah-0410</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1563,16 +1559,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/268587</t>
+          <t>https://artportalen.se/Sighting/268582</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111708705</v>
+        <v>268584</v>
       </c>
       <c r="B9" t="n">
-        <v>93223</v>
+        <v>102171</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,48 +1576,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>692</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Hårginst</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Genista pilosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källshult, Källshult, Hl</t>
+          <t>Dunkebjär, O om, skogsväg (3), Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394345</v>
+        <v>394449</v>
       </c>
       <c r="R9" t="n">
-        <v>6273040</v>
+        <v>6273360</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1646,24 +1633,24 @@
           <t>Veinge</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Arkiv-N-Lah-0416</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>1998-06-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Medobservatör Jan-Erik Cederfelt. Sparsamt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,26 +1662,535 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Skogsväg, glänta</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Halland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Arne Hansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/268584</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>268587</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102171</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>692</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Hårginst</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Genista pilosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dunkebjär, NO om, O om Dunkebjär, skogsväg, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>393876</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6273684</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Veinge</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Arkiv-N-Lah-0426</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1998-06-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1998-06-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Medobservatör Jan-Erik Cederfelt. Sparsamt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Halland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Arne Hansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/268587</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111708705</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Källshult, Källshult, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>394345</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6273040</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Laholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Veinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Sofia Fridolf</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Sofia Fridolf</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111708705</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137284586</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107865</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>626</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ljungögontröst</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Euphrasia micrantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Källshult NO, Kvarnvägen (1), Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>394775</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6272535</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Knäred</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>N-Lah-1997</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Magnusson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Erik  Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137284586</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137284638</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107865</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>626</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ljungögontröst</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Euphrasia micrantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Källshult O, Lohallavägen, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>394730</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6271595</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Knäred</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>N-Lah-2001</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Magnusson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik  Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137284638</t>
         </is>
       </c>
     </row>
@@ -1708,6 +2204,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107865</v>
+        <v>107886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107865</v>
+        <v>107886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källshult NO, Kvarnvägen (2), Hl</t>
+          <t>Källshult O, Kvarnvägen (2), Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107865</v>
+        <v>107886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107865</v>
+        <v>107886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källshult O, Lohallavägen, Hl</t>
+          <t>Källshult SO, Lohallavägen, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107886</v>
+        <v>107887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107886</v>
+        <v>107887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107886</v>
+        <v>107887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107886</v>
+        <v>107887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107887</v>
+        <v>107892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107887</v>
+        <v>107892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107887</v>
+        <v>107892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107887</v>
+        <v>107892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107892</v>
+        <v>107895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107892</v>
+        <v>107895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107892</v>
+        <v>107895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107892</v>
+        <v>107895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107895</v>
+        <v>107901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107895</v>
+        <v>107901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107895</v>
+        <v>107901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107895</v>
+        <v>107901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107901</v>
+        <v>107902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107901</v>
+        <v>107902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107901</v>
+        <v>107902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107901</v>
+        <v>107902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107902</v>
+        <v>107914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107902</v>
+        <v>107914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107902</v>
+        <v>107914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107902</v>
+        <v>107914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107914</v>
+        <v>107915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107914</v>
+        <v>107915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107914</v>
+        <v>107915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107914</v>
+        <v>107915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107915</v>
+        <v>107918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107915</v>
+        <v>107918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107915</v>
+        <v>107918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107915</v>
+        <v>107918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/S 648-2024 artfynd.xlsx
+++ b/artfynd/S 648-2024 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>137284559</v>
       </c>
       <c r="B3" t="n">
-        <v>107918</v>
+        <v>107924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137284598</v>
       </c>
       <c r="B4" t="n">
-        <v>107918</v>
+        <v>107924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>137284586</v>
       </c>
       <c r="B12" t="n">
-        <v>107918</v>
+        <v>107924</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137284638</v>
       </c>
       <c r="B13" t="n">
-        <v>107918</v>
+        <v>107924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
